--- a/robot-data/TestRNN/VSG/metrics.xlsx
+++ b/robot-data/TestRNN/VSG/metrics.xlsx
@@ -492,40 +492,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5652579082327489</v>
+        <v>-1.864104754639075</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06187525379695268</v>
+        <v>0.4077221045492772</v>
       </c>
       <c r="C2" t="n">
-        <v>17325295565051.6</v>
+        <v>47488083001443.55</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2487473694272015</v>
+        <v>0.6385312087512067</v>
       </c>
       <c r="E2" t="n">
-        <v>-63.57620002820222</v>
+        <v>-18.73648831760961</v>
       </c>
       <c r="F2" t="n">
-        <v>1.439169931142555</v>
+        <v>0.4299577742632897</v>
       </c>
       <c r="G2" t="n">
-        <v>2.072468001330729</v>
+        <v>0.9850750590974334</v>
       </c>
       <c r="H2" t="n">
-        <v>1.199654088119803</v>
+        <v>0.6557116548173364</v>
       </c>
       <c r="I2" t="n">
-        <v>-127.5049251979268</v>
+        <v>-113.2418927967847</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02735107218781365</v>
+        <v>0.02035330388681605</v>
       </c>
       <c r="K2" t="n">
-        <v>5307282047384.665</v>
+        <v>90228828493147.03</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1653815956744089</v>
+        <v>0.1426650058241896</v>
       </c>
     </row>
   </sheetData>
